--- a/backend/data/financials_by_company/0754.HK.xlsx
+++ b/backend/data/financials_by_company/0754.HK.xlsx
@@ -667,208 +667,198 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-649434500</v>
+        <v>-73365730</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.365</v>
       </c>
       <c r="D2" t="n">
-        <v>7036921000</v>
+        <v>18511082000</v>
       </c>
       <c r="E2" t="n">
-        <v>-2597738000</v>
+        <v>-201002000</v>
       </c>
       <c r="F2" t="n">
-        <v>-2597738000</v>
+        <v>-201002000</v>
       </c>
       <c r="G2" t="n">
-        <v>119582000</v>
+        <v>9759179000</v>
       </c>
       <c r="H2" t="n">
-        <v>382809000</v>
+        <v>381403000</v>
       </c>
       <c r="I2" t="n">
-        <v>28276127000</v>
+        <v>17589322000</v>
       </c>
       <c r="J2" t="n">
-        <v>4439183000</v>
+        <v>18310080000</v>
       </c>
       <c r="K2" t="n">
-        <v>4056374000</v>
+        <v>17928677000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1157879000</v>
+        <v>-1063789000</v>
       </c>
       <c r="M2" t="n">
-        <v>1250486000</v>
+        <v>1631819000</v>
       </c>
       <c r="N2" t="n">
-        <v>92607000</v>
+        <v>568030000</v>
       </c>
       <c r="O2" t="n">
-        <v>2067885500</v>
+        <v>9886815270</v>
       </c>
       <c r="P2" t="n">
-        <v>119582000</v>
+        <v>9759179000</v>
       </c>
       <c r="Q2" t="n">
-        <v>31157927000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1250000</v>
-      </c>
+        <v>24956725000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>3792541000</v>
+        <v>3818777160</v>
       </c>
       <c r="T2" t="n">
-        <v>3792541000</v>
+        <v>3818777160</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03</v>
+        <v>2.55303</v>
       </c>
       <c r="V2" t="n">
-        <v>0.03</v>
+        <v>2.55303</v>
       </c>
       <c r="W2" t="n">
-        <v>119582000</v>
+        <v>9759179000</v>
       </c>
       <c r="X2" t="n">
-        <v>119582000</v>
+        <v>9759179000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>119582000</v>
+        <v>9759179000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-983795000</v>
+        <v>-585505000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1103377000</v>
+        <v>10344684000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1103377000</v>
+        <v>10344684000</v>
       </c>
       <c r="AD2" t="n">
-        <v>1702511000</v>
+        <v>5952174000</v>
       </c>
       <c r="AE2" t="n">
-        <v>2805888000</v>
+        <v>16296858000</v>
       </c>
       <c r="AF2" t="n">
-        <v>110596000</v>
+        <v>119322000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-2597738000</v>
+        <v>-201002000</v>
       </c>
       <c r="AH2" t="n">
-        <v>486363000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1302431000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>808944000</v>
-      </c>
+        <v>201002000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>-1157879000</v>
+        <v>-1063789000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1250486000</v>
+        <v>1631819000</v>
       </c>
       <c r="AM2" t="n">
-        <v>92607000</v>
+        <v>568030000</v>
       </c>
       <c r="AN2" t="n">
-        <v>6676297000</v>
+        <v>5777471000</v>
       </c>
       <c r="AO2" t="n">
-        <v>2881800000</v>
+        <v>7367403000</v>
       </c>
       <c r="AP2" t="n">
-        <v>2880550000</v>
+        <v>7367403000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>901669000</v>
+        <v>1442246000</v>
       </c>
       <c r="AR2" t="n">
-        <v>1978881000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1250000</v>
-      </c>
+        <v>5925157000</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>9558097000</v>
+        <v>13144874000</v>
       </c>
       <c r="AU2" t="n">
-        <v>28276127000</v>
+        <v>17589322000</v>
       </c>
       <c r="AV2" t="n">
-        <v>37834224000</v>
+        <v>30734196000</v>
       </c>
       <c r="AW2" t="n">
-        <v>37834224000</v>
+        <v>30734196000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-306678500</v>
+        <v>20653421.568612</v>
       </c>
       <c r="C3" t="n">
-        <v>0.25</v>
+        <v>0.304138</v>
       </c>
       <c r="D3" t="n">
-        <v>8941385000</v>
+        <v>14885460000</v>
       </c>
       <c r="E3" t="n">
-        <v>-1226714000</v>
+        <v>67908000</v>
       </c>
       <c r="F3" t="n">
-        <v>-1226714000</v>
+        <v>67908000</v>
       </c>
       <c r="G3" t="n">
-        <v>2922321000</v>
+        <v>8762461000</v>
       </c>
       <c r="H3" t="n">
-        <v>486775000</v>
+        <v>373862000</v>
       </c>
       <c r="I3" t="n">
-        <v>24795337000</v>
+        <v>18971204000</v>
       </c>
       <c r="J3" t="n">
-        <v>7714671000</v>
+        <v>14953368000</v>
       </c>
       <c r="K3" t="n">
-        <v>7227896000</v>
+        <v>14579506000</v>
       </c>
       <c r="L3" t="n">
-        <v>-414732000</v>
+        <v>-948851000</v>
       </c>
       <c r="M3" t="n">
-        <v>933794000</v>
+        <v>1511989000</v>
       </c>
       <c r="N3" t="n">
-        <v>519062000</v>
+        <v>563138000</v>
       </c>
       <c r="O3" t="n">
-        <v>3842356500</v>
+        <v>8715206421.568611</v>
       </c>
       <c r="P3" t="n">
-        <v>2922321000</v>
+        <v>8762461000</v>
       </c>
       <c r="Q3" t="n">
-        <v>28991129000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>3762000</v>
-      </c>
+        <v>23395778000</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>3792541000</v>
       </c>
@@ -876,144 +866,146 @@
         <v>3792541000</v>
       </c>
       <c r="U3" t="n">
-        <v>0.77</v>
+        <v>2.31</v>
       </c>
       <c r="V3" t="n">
-        <v>0.77</v>
+        <v>2.31</v>
       </c>
       <c r="W3" t="n">
-        <v>2922321000</v>
+        <v>8762461000</v>
       </c>
       <c r="X3" t="n">
-        <v>2922321000</v>
+        <v>8762461000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2922321000</v>
+        <v>8762461000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-481899000</v>
+        <v>-330724000</v>
       </c>
       <c r="AB3" t="n">
-        <v>3404220000</v>
+        <v>9093185000</v>
       </c>
       <c r="AC3" t="n">
-        <v>3404220000</v>
+        <v>9093185000</v>
       </c>
       <c r="AD3" t="n">
-        <v>2889882000</v>
+        <v>3974332000</v>
       </c>
       <c r="AE3" t="n">
-        <v>6294102000</v>
+        <v>13067517000</v>
       </c>
       <c r="AF3" t="n">
-        <v>45119000</v>
+        <v>75173000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1226714000</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>-76762000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>3828000</v>
+      </c>
       <c r="AI3" t="n">
-        <v>196233000</v>
+        <v>72927000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1030481000</v>
+        <v>7000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-414732000</v>
+        <v>-948851000</v>
       </c>
       <c r="AL3" t="n">
-        <v>933794000</v>
+        <v>1511989000</v>
       </c>
       <c r="AM3" t="n">
-        <v>519062000</v>
+        <v>563138000</v>
       </c>
       <c r="AN3" t="n">
-        <v>5300680000</v>
+        <v>3856230000</v>
       </c>
       <c r="AO3" t="n">
-        <v>4195792000</v>
+        <v>4424574000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4192030000</v>
+        <v>4424574000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1905920000</v>
+        <v>1511357000</v>
       </c>
       <c r="AR3" t="n">
-        <v>2286110000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3762000</v>
-      </c>
+        <v>2913217000</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>9496472000</v>
+        <v>8280804000</v>
       </c>
       <c r="AU3" t="n">
-        <v>24795337000</v>
+        <v>18971204000</v>
       </c>
       <c r="AV3" t="n">
-        <v>34291809000</v>
+        <v>27252008000</v>
       </c>
       <c r="AW3" t="n">
-        <v>34291809000</v>
+        <v>27252008000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>20653421.568612</v>
+        <v>-306678500</v>
       </c>
       <c r="C4" t="n">
-        <v>0.304138</v>
+        <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>14885460000</v>
+        <v>8941385000</v>
       </c>
       <c r="E4" t="n">
-        <v>67908000</v>
+        <v>-1226714000</v>
       </c>
       <c r="F4" t="n">
-        <v>67908000</v>
+        <v>-1226714000</v>
       </c>
       <c r="G4" t="n">
-        <v>8762461000</v>
+        <v>2922321000</v>
       </c>
       <c r="H4" t="n">
-        <v>373862000</v>
+        <v>486775000</v>
       </c>
       <c r="I4" t="n">
-        <v>18971204000</v>
+        <v>24795337000</v>
       </c>
       <c r="J4" t="n">
-        <v>14953368000</v>
+        <v>7714671000</v>
       </c>
       <c r="K4" t="n">
-        <v>14579506000</v>
+        <v>7227896000</v>
       </c>
       <c r="L4" t="n">
-        <v>-948851000</v>
+        <v>-414732000</v>
       </c>
       <c r="M4" t="n">
-        <v>1511989000</v>
+        <v>933794000</v>
       </c>
       <c r="N4" t="n">
-        <v>563138000</v>
+        <v>519062000</v>
       </c>
       <c r="O4" t="n">
-        <v>8715206421.568611</v>
+        <v>3842356500</v>
       </c>
       <c r="P4" t="n">
-        <v>8762461000</v>
+        <v>2922321000</v>
       </c>
       <c r="Q4" t="n">
-        <v>23395778000</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>28991129000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3762000</v>
+      </c>
       <c r="S4" t="n">
         <v>3792541000</v>
       </c>
@@ -1021,230 +1013,238 @@
         <v>3792541000</v>
       </c>
       <c r="U4" t="n">
-        <v>2.31</v>
+        <v>0.77</v>
       </c>
       <c r="V4" t="n">
-        <v>2.31</v>
+        <v>0.77</v>
       </c>
       <c r="W4" t="n">
-        <v>8762461000</v>
+        <v>2922321000</v>
       </c>
       <c r="X4" t="n">
-        <v>8762461000</v>
+        <v>2922321000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>8762461000</v>
+        <v>2922321000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-330724000</v>
+        <v>-481899000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9093185000</v>
+        <v>3404220000</v>
       </c>
       <c r="AC4" t="n">
-        <v>9093185000</v>
+        <v>3404220000</v>
       </c>
       <c r="AD4" t="n">
-        <v>3974332000</v>
+        <v>2889882000</v>
       </c>
       <c r="AE4" t="n">
-        <v>13067517000</v>
+        <v>6294102000</v>
       </c>
       <c r="AF4" t="n">
-        <v>75173000</v>
+        <v>45119000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-76762000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>3828000</v>
-      </c>
+        <v>-1226714000</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>72927000</v>
+        <v>196233000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>7000</v>
+        <v>1030481000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-948851000</v>
+        <v>-414732000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1511989000</v>
+        <v>933794000</v>
       </c>
       <c r="AM4" t="n">
-        <v>563138000</v>
+        <v>519062000</v>
       </c>
       <c r="AN4" t="n">
-        <v>3856230000</v>
+        <v>5300680000</v>
       </c>
       <c r="AO4" t="n">
-        <v>4424574000</v>
+        <v>4195792000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4424574000</v>
+        <v>4192030000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1511357000</v>
+        <v>1905920000</v>
       </c>
       <c r="AR4" t="n">
-        <v>2913217000</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+        <v>2286110000</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3762000</v>
+      </c>
       <c r="AT4" t="n">
-        <v>8280804000</v>
+        <v>9496472000</v>
       </c>
       <c r="AU4" t="n">
-        <v>18971204000</v>
+        <v>24795337000</v>
       </c>
       <c r="AV4" t="n">
-        <v>27252008000</v>
+        <v>34291809000</v>
       </c>
       <c r="AW4" t="n">
-        <v>27252008000</v>
+        <v>34291809000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-73365730</v>
+        <v>-649434500</v>
       </c>
       <c r="C5" t="n">
-        <v>0.365</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>18511082000</v>
+        <v>7036921000</v>
       </c>
       <c r="E5" t="n">
-        <v>-201002000</v>
+        <v>-2597738000</v>
       </c>
       <c r="F5" t="n">
-        <v>-201002000</v>
+        <v>-2597738000</v>
       </c>
       <c r="G5" t="n">
-        <v>9759179000</v>
+        <v>119582000</v>
       </c>
       <c r="H5" t="n">
-        <v>381403000</v>
+        <v>382809000</v>
       </c>
       <c r="I5" t="n">
-        <v>17589322000</v>
+        <v>28276127000</v>
       </c>
       <c r="J5" t="n">
-        <v>18310080000</v>
+        <v>4439183000</v>
       </c>
       <c r="K5" t="n">
-        <v>17928677000</v>
+        <v>4056374000</v>
       </c>
       <c r="L5" t="n">
-        <v>-1063789000</v>
+        <v>-1157879000</v>
       </c>
       <c r="M5" t="n">
-        <v>1631819000</v>
+        <v>1250486000</v>
       </c>
       <c r="N5" t="n">
-        <v>568030000</v>
+        <v>92607000</v>
       </c>
       <c r="O5" t="n">
-        <v>9886815270</v>
+        <v>2067885500</v>
       </c>
       <c r="P5" t="n">
-        <v>9759179000</v>
+        <v>119582000</v>
       </c>
       <c r="Q5" t="n">
-        <v>24956725000</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>31157927000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1250000</v>
+      </c>
       <c r="S5" t="n">
-        <v>3818777160</v>
+        <v>3792541000</v>
       </c>
       <c r="T5" t="n">
-        <v>3818777160</v>
+        <v>3792541000</v>
       </c>
       <c r="U5" t="n">
-        <v>2.55303</v>
+        <v>0.03</v>
       </c>
       <c r="V5" t="n">
-        <v>2.55303</v>
+        <v>0.03</v>
       </c>
       <c r="W5" t="n">
-        <v>9759179000</v>
+        <v>119582000</v>
       </c>
       <c r="X5" t="n">
-        <v>9759179000</v>
+        <v>119582000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>9759179000</v>
+        <v>119582000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-585505000</v>
+        <v>-983795000</v>
       </c>
       <c r="AB5" t="n">
-        <v>10344684000</v>
+        <v>1103377000</v>
       </c>
       <c r="AC5" t="n">
-        <v>10344684000</v>
+        <v>1103377000</v>
       </c>
       <c r="AD5" t="n">
-        <v>5952174000</v>
+        <v>1702511000</v>
       </c>
       <c r="AE5" t="n">
-        <v>16296858000</v>
+        <v>2805888000</v>
       </c>
       <c r="AF5" t="n">
-        <v>119322000</v>
+        <v>110596000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-201002000</v>
+        <v>-2597738000</v>
       </c>
       <c r="AH5" t="n">
-        <v>201002000</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+        <v>486363000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1302431000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>808944000</v>
+      </c>
       <c r="AK5" t="n">
-        <v>-1063789000</v>
+        <v>-1157879000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1631819000</v>
+        <v>1250486000</v>
       </c>
       <c r="AM5" t="n">
-        <v>568030000</v>
+        <v>92607000</v>
       </c>
       <c r="AN5" t="n">
-        <v>5777471000</v>
+        <v>6676297000</v>
       </c>
       <c r="AO5" t="n">
-        <v>7367403000</v>
+        <v>2881800000</v>
       </c>
       <c r="AP5" t="n">
-        <v>7367403000</v>
+        <v>2880550000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1442246000</v>
+        <v>901669000</v>
       </c>
       <c r="AR5" t="n">
-        <v>5925157000</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+        <v>1978881000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1250000</v>
+      </c>
       <c r="AT5" t="n">
-        <v>13144874000</v>
+        <v>9558097000</v>
       </c>
       <c r="AU5" t="n">
-        <v>17589322000</v>
+        <v>28276127000</v>
       </c>
       <c r="AV5" t="n">
-        <v>30734196000</v>
+        <v>37834224000</v>
       </c>
       <c r="AW5" t="n">
-        <v>30734196000</v>
+        <v>37834224000</v>
       </c>
     </row>
   </sheetData>
@@ -1620,853 +1620,853 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>3792541000</v>
+        <v>3792540219</v>
       </c>
       <c r="C2" t="n">
-        <v>3792541000</v>
+        <v>3792540219</v>
       </c>
       <c r="D2" t="n">
-        <v>67053782000</v>
+        <v>88557325000</v>
       </c>
       <c r="E2" t="n">
-        <v>76252664000</v>
+        <v>119354802000</v>
       </c>
       <c r="F2" t="n">
-        <v>91590687000</v>
+        <v>94177471000</v>
       </c>
       <c r="G2" t="n">
-        <v>168785685000</v>
+        <v>214934197000</v>
       </c>
       <c r="H2" t="n">
-        <v>55496700000</v>
+        <v>101472312000</v>
       </c>
       <c r="I2" t="n">
-        <v>91590687000</v>
+        <v>94177471000</v>
       </c>
       <c r="J2" t="n">
-        <v>749769000</v>
+        <v>752752000</v>
       </c>
       <c r="K2" t="n">
-        <v>93282790000</v>
+        <v>96332147000</v>
       </c>
       <c r="L2" t="n">
-        <v>143748465000</v>
+        <v>183018795000</v>
       </c>
       <c r="M2" t="n">
-        <v>98915482000</v>
+        <v>113029169000</v>
       </c>
       <c r="N2" t="n">
-        <v>5632692000</v>
+        <v>16697022000</v>
       </c>
       <c r="O2" t="n">
-        <v>93282790000</v>
+        <v>96332147000</v>
       </c>
       <c r="P2" t="n">
-        <v>-1096144000</v>
+        <v>575854000</v>
       </c>
       <c r="Q2" t="n">
-        <v>85243482000</v>
+        <v>73795292000</v>
       </c>
       <c r="R2" t="n">
-        <v>15161067000</v>
+        <v>15302872000</v>
       </c>
       <c r="S2" t="n">
-        <v>379254000</v>
+        <v>237449000</v>
       </c>
       <c r="T2" t="n">
-        <v>379254000</v>
+        <v>237449000</v>
       </c>
       <c r="U2" t="n">
-        <v>157966693000</v>
+        <v>233204687000</v>
       </c>
       <c r="V2" t="n">
-        <v>66610032000</v>
+        <v>104179826000</v>
       </c>
       <c r="W2" t="n">
-        <v>1978930000</v>
+        <v>3895442000</v>
       </c>
       <c r="X2" t="n">
-        <v>13530151000</v>
+        <v>12908996000</v>
       </c>
       <c r="Y2" t="n">
-        <v>51100951000</v>
+        <v>87375388000</v>
       </c>
       <c r="Z2" t="n">
-        <v>635276000</v>
+        <v>688740000</v>
       </c>
       <c r="AA2" t="n">
-        <v>50465675000</v>
+        <v>86686648000</v>
       </c>
       <c r="AB2" t="n">
-        <v>91356661000</v>
+        <v>129024861000</v>
       </c>
       <c r="AC2" t="n">
-        <v>25151713000</v>
+        <v>31979414000</v>
       </c>
       <c r="AD2" t="n">
-        <v>114493000</v>
+        <v>64012000</v>
       </c>
       <c r="AE2" t="n">
-        <v>25037220000</v>
+        <v>31915402000</v>
       </c>
       <c r="AF2" t="n">
-        <v>34913140000</v>
+        <v>42946472000</v>
       </c>
       <c r="AG2" t="n">
-        <v>10188927000</v>
+        <v>7773249000</v>
       </c>
       <c r="AH2" t="n">
-        <v>10059383000</v>
+        <v>11172665000</v>
       </c>
       <c r="AI2" t="n">
-        <v>14664830000</v>
+        <v>24000558000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>256882175000</v>
+        <v>346233856000</v>
       </c>
       <c r="AK2" t="n">
-        <v>110028814000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>115736683000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>467884000</v>
+      </c>
       <c r="AM2" t="n">
-        <v>465751000</v>
+        <v>467884000</v>
       </c>
       <c r="AN2" t="n">
-        <v>2304951000</v>
+        <v>6389573000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1659762000</v>
+        <v>4206381000</v>
       </c>
       <c r="AP2" t="n">
-        <v>645189000</v>
+        <v>2183192000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13340525000</v>
+        <v>18841041000</v>
       </c>
       <c r="AR2" t="n">
-        <v>7263128000</v>
+        <v>8874910000</v>
       </c>
       <c r="AS2" t="n">
-        <v>6077397000</v>
+        <v>9966131000</v>
       </c>
       <c r="AT2" t="n">
-        <v>85081273000</v>
+        <v>80609222000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1692103000</v>
+        <v>2154676000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1692103000</v>
+        <v>2154676000</v>
       </c>
       <c r="AW2" t="n">
-        <v>3464682000</v>
+        <v>4510166000</v>
       </c>
       <c r="AX2" t="n">
-        <v>-2328330000</v>
+        <v>-2134358000</v>
       </c>
       <c r="AY2" t="n">
-        <v>5793012000</v>
+        <v>6644524000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>486444000</v>
+        <v>982343000</v>
       </c>
       <c r="BA2" t="n">
-        <v>3655808000</v>
+        <v>3603490000</v>
       </c>
       <c r="BB2" t="n">
-        <v>965463000</v>
+        <v>1267605000</v>
       </c>
       <c r="BC2" t="n">
-        <v>685297000</v>
-      </c>
-      <c r="BD2" t="inlineStr"/>
+        <v>791086000</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1587108000</v>
+      </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1203384000</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
+        <v>2283003000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>42684188000</v>
+      </c>
       <c r="BH2" t="n">
-        <v>871219000</v>
+        <v>1919188000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2949035000</v>
+        <v>6267556000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>16637219000</v>
+        <v>39214123000</v>
       </c>
       <c r="BK2" t="n">
-        <v>100498401000</v>
+        <v>125075873000</v>
       </c>
       <c r="BL2" t="n">
-        <v>100498401000</v>
+        <v>125075873000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11675054000</v>
+        <v>14676248000</v>
       </c>
       <c r="BN2" t="n">
-        <v>4058715000</v>
+        <v>4882649000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-534497000</v>
+        <v>-185667000</v>
       </c>
       <c r="BP2" t="n">
-        <v>4593212000</v>
+        <v>5068316000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8960334000</v>
+        <v>36178533000</v>
       </c>
       <c r="BR2" t="n">
-        <v>511221000</v>
+        <v>6133808000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8449113000</v>
+        <v>30044725000</v>
       </c>
       <c r="BT2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>3792541000</v>
+        <v>3792540572</v>
       </c>
       <c r="C3" t="n">
-        <v>3792541000</v>
+        <v>3792540572</v>
       </c>
       <c r="D3" t="n">
-        <v>76325524000</v>
+        <v>83443675000</v>
       </c>
       <c r="E3" t="n">
-        <v>88474290000</v>
+        <v>98541412000</v>
       </c>
       <c r="F3" t="n">
-        <v>93520885000</v>
+        <v>91207883000</v>
       </c>
       <c r="G3" t="n">
-        <v>183042050000</v>
+        <v>190702298000</v>
       </c>
       <c r="H3" t="n">
-        <v>52319403000</v>
+        <v>71562469000</v>
       </c>
       <c r="I3" t="n">
-        <v>93520885000</v>
+        <v>91207883000</v>
       </c>
       <c r="J3" t="n">
-        <v>790453000</v>
+        <v>988874000</v>
       </c>
       <c r="K3" t="n">
-        <v>95358213000</v>
+        <v>93149760000</v>
       </c>
       <c r="L3" t="n">
-        <v>145183224000</v>
+        <v>164756818000</v>
       </c>
       <c r="M3" t="n">
-        <v>100984849000</v>
+        <v>98378166000</v>
       </c>
       <c r="N3" t="n">
-        <v>5626636000</v>
+        <v>5228406000</v>
       </c>
       <c r="O3" t="n">
-        <v>95358213000</v>
+        <v>93149760000</v>
       </c>
       <c r="P3" t="n">
-        <v>-654011000</v>
+        <v>123157000</v>
       </c>
       <c r="Q3" t="n">
-        <v>85123900000</v>
+        <v>82201579000</v>
       </c>
       <c r="R3" t="n">
-        <v>15161067000</v>
+        <v>15253007000</v>
       </c>
       <c r="S3" t="n">
-        <v>379254000</v>
+        <v>287314000</v>
       </c>
       <c r="T3" t="n">
-        <v>379254000</v>
+        <v>287314000</v>
       </c>
       <c r="U3" t="n">
-        <v>187709286000</v>
+        <v>200336235000</v>
       </c>
       <c r="V3" t="n">
-        <v>66870501000</v>
+        <v>88677103000</v>
       </c>
       <c r="W3" t="n">
-        <v>2040007000</v>
+        <v>2437475000</v>
       </c>
       <c r="X3" t="n">
-        <v>14307544000</v>
+        <v>14045565000</v>
       </c>
       <c r="Y3" t="n">
-        <v>50522950000</v>
+        <v>72194063000</v>
       </c>
       <c r="Z3" t="n">
-        <v>697939000</v>
+        <v>587005000</v>
       </c>
       <c r="AA3" t="n">
-        <v>49825011000</v>
+        <v>71607058000</v>
       </c>
       <c r="AB3" t="n">
-        <v>120838785000</v>
+        <v>111659132000</v>
       </c>
       <c r="AC3" t="n">
-        <v>37951340000</v>
+        <v>26347349000</v>
       </c>
       <c r="AD3" t="n">
-        <v>92514000</v>
+        <v>401869000</v>
       </c>
       <c r="AE3" t="n">
-        <v>37858826000</v>
+        <v>25945480000</v>
       </c>
       <c r="AF3" t="n">
-        <v>32388105000</v>
+        <v>34639870000</v>
       </c>
       <c r="AG3" t="n">
-        <v>7172849000</v>
+        <v>6798950000</v>
       </c>
       <c r="AH3" t="n">
-        <v>10548422000</v>
+        <v>10737968000</v>
       </c>
       <c r="AI3" t="n">
-        <v>14666834000</v>
+        <v>17102952000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>288694135000</v>
+        <v>298714401000</v>
       </c>
       <c r="AK3" t="n">
-        <v>115535947000</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
+        <v>115492800000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>467805000</v>
+      </c>
       <c r="AM3" t="n">
-        <v>468939000</v>
+        <v>467805000</v>
       </c>
       <c r="AN3" t="n">
-        <v>2872261000</v>
+        <v>4751471000</v>
       </c>
       <c r="AO3" t="n">
-        <v>2093459000</v>
+        <v>3562352000</v>
       </c>
       <c r="AP3" t="n">
-        <v>778802000</v>
+        <v>1189119000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15557291000</v>
+        <v>17195754000</v>
       </c>
       <c r="AR3" t="n">
-        <v>8392676000</v>
+        <v>8678918000</v>
       </c>
       <c r="AS3" t="n">
-        <v>7164615000</v>
+        <v>8516836000</v>
       </c>
       <c r="AT3" t="n">
-        <v>87275592000</v>
+        <v>83834452000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1837328000</v>
+        <v>1941877000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1837328000</v>
+        <v>1941877000</v>
       </c>
       <c r="AW3" t="n">
-        <v>3544893000</v>
+        <v>3913801000</v>
       </c>
       <c r="AX3" t="n">
-        <v>-2102438000</v>
+        <v>-1945130000</v>
       </c>
       <c r="AY3" t="n">
-        <v>5647331000</v>
+        <v>5858931000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>394291000</v>
+        <v>883302000</v>
       </c>
       <c r="BA3" t="n">
-        <v>3701769000</v>
+        <v>3328216000</v>
       </c>
       <c r="BB3" t="n">
-        <v>917456000</v>
+        <v>947511000</v>
       </c>
       <c r="BC3" t="n">
-        <v>633815000</v>
+        <v>699902000</v>
       </c>
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1744497000</v>
-      </c>
-      <c r="BG3" t="inlineStr"/>
+        <v>1701476000</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>36501625000</v>
+      </c>
       <c r="BH3" t="n">
-        <v>1424841000</v>
+        <v>1619534000</v>
       </c>
       <c r="BI3" t="n">
-        <v>4010019000</v>
+        <v>4285354000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>17425261000</v>
+        <v>33567499000</v>
       </c>
       <c r="BK3" t="n">
-        <v>119755954000</v>
+        <v>114212724000</v>
       </c>
       <c r="BL3" t="n">
-        <v>119755954000</v>
+        <v>114212724000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12077186000</v>
+        <v>7650555000</v>
       </c>
       <c r="BN3" t="n">
-        <v>4129782000</v>
+        <v>4622198000</v>
       </c>
       <c r="BO3" t="n">
-        <v>-246241000</v>
+        <v>-224405000</v>
       </c>
       <c r="BP3" t="n">
-        <v>4376023000</v>
+        <v>4846603000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>12590648000</v>
+        <v>15562261000</v>
       </c>
       <c r="BR3" t="n">
-        <v>1232335000</v>
+        <v>1453398000</v>
       </c>
       <c r="BS3" t="n">
-        <v>11358313000</v>
-      </c>
-      <c r="BT3" t="inlineStr"/>
+        <v>14108863000</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>18394217000</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>3792540572</v>
+        <v>3792541000</v>
       </c>
       <c r="C4" t="n">
-        <v>3792540572</v>
+        <v>3792541000</v>
       </c>
       <c r="D4" t="n">
-        <v>83443675000</v>
+        <v>76325524000</v>
       </c>
       <c r="E4" t="n">
-        <v>98541412000</v>
+        <v>88474290000</v>
       </c>
       <c r="F4" t="n">
-        <v>91207883000</v>
+        <v>93520885000</v>
       </c>
       <c r="G4" t="n">
-        <v>190702298000</v>
+        <v>183042050000</v>
       </c>
       <c r="H4" t="n">
-        <v>71562469000</v>
+        <v>52319403000</v>
       </c>
       <c r="I4" t="n">
-        <v>91207883000</v>
+        <v>93520885000</v>
       </c>
       <c r="J4" t="n">
-        <v>988874000</v>
+        <v>790453000</v>
       </c>
       <c r="K4" t="n">
-        <v>93149760000</v>
+        <v>95358213000</v>
       </c>
       <c r="L4" t="n">
-        <v>164756818000</v>
+        <v>145183224000</v>
       </c>
       <c r="M4" t="n">
-        <v>98378166000</v>
+        <v>100984849000</v>
       </c>
       <c r="N4" t="n">
-        <v>5228406000</v>
+        <v>5626636000</v>
       </c>
       <c r="O4" t="n">
-        <v>93149760000</v>
+        <v>95358213000</v>
       </c>
       <c r="P4" t="n">
-        <v>123157000</v>
+        <v>-654011000</v>
       </c>
       <c r="Q4" t="n">
-        <v>82201579000</v>
+        <v>85123900000</v>
       </c>
       <c r="R4" t="n">
-        <v>15253007000</v>
+        <v>15161067000</v>
       </c>
       <c r="S4" t="n">
-        <v>287314000</v>
+        <v>379254000</v>
       </c>
       <c r="T4" t="n">
-        <v>287314000</v>
+        <v>379254000</v>
       </c>
       <c r="U4" t="n">
-        <v>200336235000</v>
+        <v>187709286000</v>
       </c>
       <c r="V4" t="n">
-        <v>88677103000</v>
+        <v>66870501000</v>
       </c>
       <c r="W4" t="n">
-        <v>2437475000</v>
+        <v>2040007000</v>
       </c>
       <c r="X4" t="n">
-        <v>14045565000</v>
+        <v>14307544000</v>
       </c>
       <c r="Y4" t="n">
-        <v>72194063000</v>
+        <v>50522950000</v>
       </c>
       <c r="Z4" t="n">
-        <v>587005000</v>
+        <v>697939000</v>
       </c>
       <c r="AA4" t="n">
-        <v>71607058000</v>
+        <v>49825011000</v>
       </c>
       <c r="AB4" t="n">
-        <v>111659132000</v>
+        <v>120838785000</v>
       </c>
       <c r="AC4" t="n">
-        <v>26347349000</v>
+        <v>37951340000</v>
       </c>
       <c r="AD4" t="n">
-        <v>401869000</v>
+        <v>92514000</v>
       </c>
       <c r="AE4" t="n">
-        <v>25945480000</v>
+        <v>37858826000</v>
       </c>
       <c r="AF4" t="n">
-        <v>34639870000</v>
+        <v>32388105000</v>
       </c>
       <c r="AG4" t="n">
-        <v>6798950000</v>
+        <v>7172849000</v>
       </c>
       <c r="AH4" t="n">
-        <v>10737968000</v>
+        <v>10548422000</v>
       </c>
       <c r="AI4" t="n">
-        <v>17102952000</v>
+        <v>14666834000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>298714401000</v>
+        <v>288694135000</v>
       </c>
       <c r="AK4" t="n">
-        <v>115492800000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>467805000</v>
-      </c>
+        <v>115535947000</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>467805000</v>
+        <v>468939000</v>
       </c>
       <c r="AN4" t="n">
-        <v>4751471000</v>
+        <v>2872261000</v>
       </c>
       <c r="AO4" t="n">
-        <v>3562352000</v>
+        <v>2093459000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1189119000</v>
+        <v>778802000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17195754000</v>
+        <v>15557291000</v>
       </c>
       <c r="AR4" t="n">
-        <v>8678918000</v>
+        <v>8392676000</v>
       </c>
       <c r="AS4" t="n">
-        <v>8516836000</v>
+        <v>7164615000</v>
       </c>
       <c r="AT4" t="n">
-        <v>83834452000</v>
+        <v>87275592000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1941877000</v>
+        <v>1837328000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1941877000</v>
+        <v>1837328000</v>
       </c>
       <c r="AW4" t="n">
-        <v>3913801000</v>
+        <v>3544893000</v>
       </c>
       <c r="AX4" t="n">
-        <v>-1945130000</v>
+        <v>-2102438000</v>
       </c>
       <c r="AY4" t="n">
-        <v>5858931000</v>
+        <v>5647331000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>883302000</v>
+        <v>394291000</v>
       </c>
       <c r="BA4" t="n">
-        <v>3328216000</v>
+        <v>3701769000</v>
       </c>
       <c r="BB4" t="n">
-        <v>947511000</v>
+        <v>917456000</v>
       </c>
       <c r="BC4" t="n">
-        <v>699902000</v>
+        <v>633815000</v>
       </c>
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1701476000</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>36501625000</v>
-      </c>
+        <v>1744497000</v>
+      </c>
+      <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
-        <v>1619534000</v>
+        <v>1424841000</v>
       </c>
       <c r="BI4" t="n">
-        <v>4285354000</v>
+        <v>4010019000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>33567499000</v>
+        <v>17425261000</v>
       </c>
       <c r="BK4" t="n">
-        <v>114212724000</v>
+        <v>119755954000</v>
       </c>
       <c r="BL4" t="n">
-        <v>114212724000</v>
+        <v>119755954000</v>
       </c>
       <c r="BM4" t="n">
-        <v>7650555000</v>
+        <v>12077186000</v>
       </c>
       <c r="BN4" t="n">
-        <v>4622198000</v>
+        <v>4129782000</v>
       </c>
       <c r="BO4" t="n">
-        <v>-224405000</v>
+        <v>-246241000</v>
       </c>
       <c r="BP4" t="n">
-        <v>4846603000</v>
+        <v>4376023000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>15562261000</v>
+        <v>12590648000</v>
       </c>
       <c r="BR4" t="n">
-        <v>1453398000</v>
+        <v>1232335000</v>
       </c>
       <c r="BS4" t="n">
-        <v>14108863000</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>18394217000</v>
-      </c>
+        <v>11358313000</v>
+      </c>
+      <c r="BT4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>3792540219</v>
+        <v>3792541000</v>
       </c>
       <c r="C5" t="n">
-        <v>3792540219</v>
+        <v>3792541000</v>
       </c>
       <c r="D5" t="n">
-        <v>88557325000</v>
+        <v>67053782000</v>
       </c>
       <c r="E5" t="n">
-        <v>119354802000</v>
+        <v>76252664000</v>
       </c>
       <c r="F5" t="n">
-        <v>94177471000</v>
+        <v>91590687000</v>
       </c>
       <c r="G5" t="n">
-        <v>214934197000</v>
+        <v>168785685000</v>
       </c>
       <c r="H5" t="n">
-        <v>101472312000</v>
+        <v>55496700000</v>
       </c>
       <c r="I5" t="n">
-        <v>94177471000</v>
+        <v>91590687000</v>
       </c>
       <c r="J5" t="n">
-        <v>752752000</v>
+        <v>749769000</v>
       </c>
       <c r="K5" t="n">
-        <v>96332147000</v>
+        <v>93282790000</v>
       </c>
       <c r="L5" t="n">
-        <v>183018795000</v>
+        <v>143748465000</v>
       </c>
       <c r="M5" t="n">
-        <v>113029169000</v>
+        <v>98915482000</v>
       </c>
       <c r="N5" t="n">
-        <v>16697022000</v>
+        <v>5632692000</v>
       </c>
       <c r="O5" t="n">
-        <v>96332147000</v>
+        <v>93282790000</v>
       </c>
       <c r="P5" t="n">
-        <v>575854000</v>
+        <v>-1096144000</v>
       </c>
       <c r="Q5" t="n">
-        <v>73795292000</v>
+        <v>85243482000</v>
       </c>
       <c r="R5" t="n">
-        <v>15302872000</v>
+        <v>15161067000</v>
       </c>
       <c r="S5" t="n">
-        <v>237449000</v>
+        <v>379254000</v>
       </c>
       <c r="T5" t="n">
-        <v>237449000</v>
+        <v>379254000</v>
       </c>
       <c r="U5" t="n">
-        <v>233204687000</v>
+        <v>157966693000</v>
       </c>
       <c r="V5" t="n">
-        <v>104179826000</v>
+        <v>66610032000</v>
       </c>
       <c r="W5" t="n">
-        <v>3895442000</v>
+        <v>1978930000</v>
       </c>
       <c r="X5" t="n">
-        <v>12908996000</v>
+        <v>13530151000</v>
       </c>
       <c r="Y5" t="n">
-        <v>87375388000</v>
+        <v>51100951000</v>
       </c>
       <c r="Z5" t="n">
-        <v>688740000</v>
+        <v>635276000</v>
       </c>
       <c r="AA5" t="n">
-        <v>86686648000</v>
+        <v>50465675000</v>
       </c>
       <c r="AB5" t="n">
-        <v>129024861000</v>
+        <v>91356661000</v>
       </c>
       <c r="AC5" t="n">
-        <v>31979414000</v>
+        <v>25151713000</v>
       </c>
       <c r="AD5" t="n">
-        <v>64012000</v>
+        <v>114493000</v>
       </c>
       <c r="AE5" t="n">
-        <v>31915402000</v>
+        <v>25037220000</v>
       </c>
       <c r="AF5" t="n">
-        <v>42946472000</v>
+        <v>34913140000</v>
       </c>
       <c r="AG5" t="n">
-        <v>7773249000</v>
+        <v>10188927000</v>
       </c>
       <c r="AH5" t="n">
-        <v>11172665000</v>
+        <v>10059383000</v>
       </c>
       <c r="AI5" t="n">
-        <v>24000558000</v>
+        <v>14664830000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>346233856000</v>
+        <v>256882175000</v>
       </c>
       <c r="AK5" t="n">
-        <v>115736683000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>467884000</v>
-      </c>
+        <v>110028814000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>467884000</v>
+        <v>465751000</v>
       </c>
       <c r="AN5" t="n">
-        <v>6389573000</v>
+        <v>2304951000</v>
       </c>
       <c r="AO5" t="n">
-        <v>4206381000</v>
+        <v>1659762000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2183192000</v>
+        <v>645189000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18841041000</v>
+        <v>13340525000</v>
       </c>
       <c r="AR5" t="n">
-        <v>8874910000</v>
+        <v>7263128000</v>
       </c>
       <c r="AS5" t="n">
-        <v>9966131000</v>
+        <v>6077397000</v>
       </c>
       <c r="AT5" t="n">
-        <v>80609222000</v>
+        <v>85081273000</v>
       </c>
       <c r="AU5" t="n">
-        <v>2154676000</v>
+        <v>1692103000</v>
       </c>
       <c r="AV5" t="n">
-        <v>2154676000</v>
+        <v>1692103000</v>
       </c>
       <c r="AW5" t="n">
-        <v>4510166000</v>
+        <v>3464682000</v>
       </c>
       <c r="AX5" t="n">
-        <v>-2134358000</v>
+        <v>-2328330000</v>
       </c>
       <c r="AY5" t="n">
-        <v>6644524000</v>
+        <v>5793012000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>982343000</v>
+        <v>486444000</v>
       </c>
       <c r="BA5" t="n">
-        <v>3603490000</v>
+        <v>3655808000</v>
       </c>
       <c r="BB5" t="n">
-        <v>1267605000</v>
+        <v>965463000</v>
       </c>
       <c r="BC5" t="n">
-        <v>791086000</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1587108000</v>
-      </c>
+        <v>685297000</v>
+      </c>
+      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>2283003000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>42684188000</v>
-      </c>
+        <v>1203384000</v>
+      </c>
+      <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="n">
-        <v>1919188000</v>
+        <v>871219000</v>
       </c>
       <c r="BI5" t="n">
-        <v>6267556000</v>
+        <v>2949035000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>39214123000</v>
+        <v>16637219000</v>
       </c>
       <c r="BK5" t="n">
-        <v>125075873000</v>
+        <v>100498401000</v>
       </c>
       <c r="BL5" t="n">
-        <v>125075873000</v>
+        <v>100498401000</v>
       </c>
       <c r="BM5" t="n">
-        <v>14676248000</v>
+        <v>11675054000</v>
       </c>
       <c r="BN5" t="n">
-        <v>4882649000</v>
+        <v>4058715000</v>
       </c>
       <c r="BO5" t="n">
-        <v>-185667000</v>
+        <v>-534497000</v>
       </c>
       <c r="BP5" t="n">
-        <v>5068316000</v>
+        <v>4593212000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>36178533000</v>
+        <v>8960334000</v>
       </c>
       <c r="BR5" t="n">
-        <v>6133808000</v>
+        <v>511221000</v>
       </c>
       <c r="BS5" t="n">
-        <v>30044725000</v>
+        <v>8449113000</v>
       </c>
       <c r="BT5" t="inlineStr"/>
     </row>
@@ -2778,684 +2778,684 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>8501098000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>21097992000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-897943000</v>
+      </c>
       <c r="D2" t="n">
-        <v>-27750310000</v>
+        <v>-48337828000</v>
       </c>
       <c r="E2" t="n">
-        <v>17190892000</v>
+        <v>46905522000</v>
       </c>
       <c r="F2" t="n">
-        <v>-207518000</v>
+        <v>-369024000</v>
       </c>
       <c r="G2" t="n">
-        <v>8449113000</v>
+        <v>30044725000</v>
       </c>
       <c r="H2" t="n">
-        <v>11358313000</v>
+        <v>27908584000</v>
       </c>
       <c r="I2" t="n">
-        <v>-214262000</v>
+        <v>839660000</v>
       </c>
       <c r="J2" t="n">
-        <v>-2694938000</v>
+        <v>1296481000</v>
       </c>
       <c r="K2" t="n">
-        <v>-16021416000</v>
+        <v>-12149772000</v>
       </c>
       <c r="L2" t="n">
-        <v>-842532000</v>
+        <v>1988779000</v>
       </c>
       <c r="M2" t="n">
-        <v>-4501523000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+        <v>-8264794000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-3479289000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-3479289000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-897943000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-897943000</v>
+      </c>
       <c r="R2" t="n">
-        <v>-10559418000</v>
+        <v>-1432306000</v>
       </c>
       <c r="S2" t="n">
-        <v>-384594000</v>
+        <v>-5212908000</v>
       </c>
       <c r="T2" t="n">
-        <v>-384594000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
+        <v>-5954102000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>741194000</v>
+      </c>
       <c r="V2" t="n">
-        <v>-10174824000</v>
+        <v>3780602000</v>
       </c>
       <c r="W2" t="n">
-        <v>-27365716000</v>
+        <v>-42383726000</v>
       </c>
       <c r="X2" t="n">
-        <v>17190892000</v>
+        <v>46164328000</v>
       </c>
       <c r="Y2" t="n">
-        <v>4617862000</v>
+        <v>-8020763000</v>
       </c>
       <c r="Z2" t="n">
-        <v>1697068000</v>
+        <v>-4410008000</v>
       </c>
       <c r="AA2" t="n">
-        <v>163732000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>30598000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>30598000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
       <c r="AE2" t="n">
-        <v>440897000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>976566000</v>
-      </c>
+        <v>-537961000</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>-535669000</v>
+        <v>-537961000</v>
       </c>
       <c r="AH2" t="n">
-        <v>23583000</v>
+        <v>-2278228000</v>
       </c>
       <c r="AI2" t="n">
-        <v>23583000</v>
+        <v>1272812000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-2278228000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-5745000</v>
+        <v>-94110000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-5745000</v>
+        <v>-94110000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-201773000</v>
+        <v>-274914000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-201773000</v>
+        <v>-274914000</v>
       </c>
       <c r="AO2" t="n">
-        <v>8708616000</v>
+        <v>21467016000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1360678000</v>
+        <v>-3895765000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>92607000</v>
+        <v>562936000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-43409000</v>
+        <v>-35574000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1537244000</v>
+        <v>10969258000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-17720429000</v>
+        <v>12554030000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-1069225000</v>
+        <v>10544324000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1025456000</v>
+        <v>-4345130000</v>
       </c>
       <c r="AW2" t="n">
-        <v>20310403000</v>
+        <v>-5501551000</v>
       </c>
       <c r="AX2" t="n">
-        <v>-1008961000</v>
+        <v>-2282415000</v>
       </c>
       <c r="AY2" t="n">
-        <v>1157879000</v>
+        <v>1264791000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>382809000</v>
+        <v>381403000</v>
       </c>
       <c r="BA2" t="n">
-        <v>71919000</v>
+        <v>58216000</v>
       </c>
       <c r="BB2" t="n">
-        <v>310890000</v>
+        <v>323187000</v>
       </c>
       <c r="BC2" t="n">
-        <v>163650000</v>
+        <v>-7066259000</v>
       </c>
       <c r="BD2" t="n">
-        <v>1102000</v>
+        <v>-172200000</v>
       </c>
       <c r="BE2" t="n">
-        <v>5076000</v>
+        <v>-230000</v>
       </c>
       <c r="BF2" t="n">
-        <v>486363000</v>
+        <v>1195000</v>
       </c>
       <c r="BG2" t="n">
-        <v>2805888000</v>
+        <v>16296858000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>15673364000</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>17953664000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
       <c r="D3" t="n">
-        <v>-22272722000</v>
+        <v>-45056464000</v>
       </c>
       <c r="E3" t="n">
-        <v>11554664000</v>
+        <v>32258842000</v>
       </c>
       <c r="F3" t="n">
-        <v>-158117000</v>
+        <v>-157446000</v>
       </c>
       <c r="G3" t="n">
-        <v>11358313000</v>
+        <v>14108863000</v>
       </c>
       <c r="H3" t="n">
-        <v>14108863000</v>
+        <v>30044725000</v>
       </c>
       <c r="I3" t="n">
-        <v>-183273000</v>
+        <v>-1952867000</v>
       </c>
       <c r="J3" t="n">
-        <v>-2567277000</v>
+        <v>-13982995000</v>
       </c>
       <c r="K3" t="n">
-        <v>-16901054000</v>
+        <v>-34078228000</v>
       </c>
       <c r="L3" t="n">
-        <v>-566451000</v>
+        <v>-13515591000</v>
       </c>
       <c r="M3" t="n">
-        <v>-5476372000</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>-7348798000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-356174000</v>
+      </c>
       <c r="O3" t="n">
+        <v>-356174000</v>
+      </c>
+      <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
       <c r="R3" t="n">
-        <v>-10718058000</v>
+        <v>-12797622000</v>
       </c>
       <c r="S3" t="n">
-        <v>-2118046000</v>
+        <v>-277615000</v>
       </c>
       <c r="T3" t="n">
-        <v>-2118046000</v>
+        <v>-2171223000</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1893608000</v>
       </c>
       <c r="V3" t="n">
-        <v>-8600012000</v>
+        <v>-12520007000</v>
       </c>
       <c r="W3" t="n">
-        <v>-20154676000</v>
+        <v>-42885241000</v>
       </c>
       <c r="X3" t="n">
-        <v>11554664000</v>
+        <v>30365234000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1497704000</v>
+        <v>1984123000</v>
       </c>
       <c r="Z3" t="n">
-        <v>215637000</v>
+        <v>1515458000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>5396000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5396000</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>893128000</v>
+        <v>-46942000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1927086000</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1033958000</v>
+        <v>-46942000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-333924000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>139657000</v>
-      </c>
+        <v>-407470000</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>-473581000</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-52374000</v>
+        <v>-74321000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-52374000</v>
+        <v>-74321000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-105743000</v>
+        <v>-83125000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-105743000</v>
+        <v>-83125000</v>
       </c>
       <c r="AO3" t="n">
-        <v>15831481000</v>
+        <v>18111110000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1719836000</v>
+        <v>-2612712000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>519062000</v>
+        <v>558183000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-54668000</v>
+        <v>-32728000</v>
       </c>
       <c r="AS3" t="n">
-        <v>10587397000</v>
+        <v>10227098000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-672868000</v>
+        <v>9574647000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-1269468000</v>
+        <v>-8715101000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-3104863000</v>
+        <v>5405823000</v>
       </c>
       <c r="AW3" t="n">
-        <v>15239370000</v>
+        <v>4168546000</v>
       </c>
       <c r="AX3" t="n">
-        <v>395226000</v>
+        <v>-206817000</v>
       </c>
       <c r="AY3" t="n">
-        <v>414732000</v>
+        <v>952679000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>486775000</v>
+        <v>373862000</v>
       </c>
       <c r="BA3" t="n">
-        <v>83024000</v>
+        <v>56210000</v>
       </c>
       <c r="BB3" t="n">
-        <v>403751000</v>
+        <v>317652000</v>
       </c>
       <c r="BC3" t="n">
-        <v>-2137276000</v>
+        <v>-7634545000</v>
       </c>
       <c r="BD3" t="n">
-        <v>14051000</v>
+        <v>17375000</v>
       </c>
       <c r="BE3" t="n">
-        <v>75673000</v>
+        <v>18983000</v>
       </c>
       <c r="BF3" t="n">
-        <v>-2235000</v>
+        <v>868000</v>
       </c>
       <c r="BG3" t="n">
-        <v>6294102000</v>
+        <v>13067517000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>17953664000</v>
-      </c>
-      <c r="C4" t="n">
+        <v>15673364000</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>-22272722000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11554664000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-158117000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11358313000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>14108863000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-183273000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-2567277000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-16901054000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-566451000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-5476372000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="n">
-        <v>-45056464000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>32258842000</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-157446000</v>
-      </c>
-      <c r="G4" t="n">
-        <v>14108863000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>30044725000</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-1952867000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-13982995000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-34078228000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-13515591000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-7348798000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-356174000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-356174000</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>-10718058000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-2118046000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-2118046000</v>
+      </c>
+      <c r="U4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="V4" t="n">
+        <v>-8600012000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-20154676000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>11554664000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-1497704000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>215637000</v>
+      </c>
+      <c r="AA4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
-        <v>-12797622000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-277615000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-2171223000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1893608000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-12520007000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-42885241000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>30365234000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1984123000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1515458000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>150000</v>
-      </c>
       <c r="AB4" t="n">
-        <v>5396000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>5396000</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>-46942000</v>
+        <v>893128000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1927086000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-46942000</v>
+        <v>-1033958000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-407470000</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
+        <v>-333924000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>139657000</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-473581000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-74321000</v>
+        <v>-52374000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-74321000</v>
+        <v>-52374000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-83125000</v>
+        <v>-105743000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-83125000</v>
+        <v>-105743000</v>
       </c>
       <c r="AO4" t="n">
-        <v>18111110000</v>
+        <v>15831481000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-2612712000</v>
+        <v>-1719836000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>558183000</v>
+        <v>519062000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-32728000</v>
+        <v>-54668000</v>
       </c>
       <c r="AS4" t="n">
-        <v>10227098000</v>
+        <v>10587397000</v>
       </c>
       <c r="AT4" t="n">
-        <v>9574647000</v>
+        <v>-672868000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-8715101000</v>
+        <v>-1269468000</v>
       </c>
       <c r="AV4" t="n">
-        <v>5405823000</v>
+        <v>-3104863000</v>
       </c>
       <c r="AW4" t="n">
-        <v>4168546000</v>
+        <v>15239370000</v>
       </c>
       <c r="AX4" t="n">
-        <v>-206817000</v>
+        <v>395226000</v>
       </c>
       <c r="AY4" t="n">
-        <v>952679000</v>
+        <v>414732000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>373862000</v>
+        <v>486775000</v>
       </c>
       <c r="BA4" t="n">
-        <v>56210000</v>
+        <v>83024000</v>
       </c>
       <c r="BB4" t="n">
-        <v>317652000</v>
+        <v>403751000</v>
       </c>
       <c r="BC4" t="n">
-        <v>-7634545000</v>
+        <v>-2137276000</v>
       </c>
       <c r="BD4" t="n">
-        <v>17375000</v>
+        <v>14051000</v>
       </c>
       <c r="BE4" t="n">
-        <v>18983000</v>
+        <v>75673000</v>
       </c>
       <c r="BF4" t="n">
-        <v>868000</v>
+        <v>-2235000</v>
       </c>
       <c r="BG4" t="n">
-        <v>13067517000</v>
+        <v>6294102000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>21097992000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-897943000</v>
-      </c>
+        <v>8501098000</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>-48337828000</v>
+        <v>-27750310000</v>
       </c>
       <c r="E5" t="n">
-        <v>46905522000</v>
+        <v>17190892000</v>
       </c>
       <c r="F5" t="n">
-        <v>-369024000</v>
+        <v>-207518000</v>
       </c>
       <c r="G5" t="n">
-        <v>30044725000</v>
+        <v>8449113000</v>
       </c>
       <c r="H5" t="n">
-        <v>27908584000</v>
+        <v>11358313000</v>
       </c>
       <c r="I5" t="n">
-        <v>839660000</v>
+        <v>-214262000</v>
       </c>
       <c r="J5" t="n">
-        <v>1296481000</v>
+        <v>-2694938000</v>
       </c>
       <c r="K5" t="n">
-        <v>-12149772000</v>
+        <v>-16021416000</v>
       </c>
       <c r="L5" t="n">
-        <v>1988779000</v>
+        <v>-842532000</v>
       </c>
       <c r="M5" t="n">
-        <v>-8264794000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-3479289000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-3479289000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-897943000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-897943000</v>
-      </c>
+        <v>-4501523000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>-1432306000</v>
+        <v>-10559418000</v>
       </c>
       <c r="S5" t="n">
-        <v>-5212908000</v>
+        <v>-384594000</v>
       </c>
       <c r="T5" t="n">
-        <v>-5954102000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>741194000</v>
-      </c>
+        <v>-384594000</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>3780602000</v>
+        <v>-10174824000</v>
       </c>
       <c r="W5" t="n">
-        <v>-42383726000</v>
+        <v>-27365716000</v>
       </c>
       <c r="X5" t="n">
-        <v>46164328000</v>
+        <v>17190892000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-8020763000</v>
+        <v>4617862000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-4410008000</v>
+        <v>1697068000</v>
       </c>
       <c r="AA5" t="n">
+        <v>163732000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>440897000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>976566000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-535669000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>23583000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>23583000</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>0</v>
       </c>
-      <c r="AB5" t="n">
-        <v>30598000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>30598000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-537961000</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="n">
-        <v>-537961000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-2278228000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1272812000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-2278228000</v>
-      </c>
       <c r="AK5" t="n">
-        <v>-94110000</v>
+        <v>-5745000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-94110000</v>
+        <v>-5745000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-274914000</v>
+        <v>-201773000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-274914000</v>
+        <v>-201773000</v>
       </c>
       <c r="AO5" t="n">
-        <v>21467016000</v>
+        <v>8708616000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-3895765000</v>
+        <v>-1360678000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>562936000</v>
+        <v>92607000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-35574000</v>
+        <v>-43409000</v>
       </c>
       <c r="AS5" t="n">
-        <v>10969258000</v>
+        <v>1537244000</v>
       </c>
       <c r="AT5" t="n">
-        <v>12554030000</v>
+        <v>-17720429000</v>
       </c>
       <c r="AU5" t="n">
-        <v>10544324000</v>
+        <v>-1069225000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-4345130000</v>
+        <v>1025456000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-5501551000</v>
+        <v>20310403000</v>
       </c>
       <c r="AX5" t="n">
-        <v>-2282415000</v>
+        <v>-1008961000</v>
       </c>
       <c r="AY5" t="n">
-        <v>1264791000</v>
+        <v>1157879000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>381403000</v>
+        <v>382809000</v>
       </c>
       <c r="BA5" t="n">
-        <v>58216000</v>
+        <v>71919000</v>
       </c>
       <c r="BB5" t="n">
-        <v>323187000</v>
+        <v>310890000</v>
       </c>
       <c r="BC5" t="n">
-        <v>-7066259000</v>
+        <v>163650000</v>
       </c>
       <c r="BD5" t="n">
-        <v>-172200000</v>
+        <v>1102000</v>
       </c>
       <c r="BE5" t="n">
-        <v>-230000</v>
+        <v>5076000</v>
       </c>
       <c r="BF5" t="n">
-        <v>1195000</v>
+        <v>486363000</v>
       </c>
       <c r="BG5" t="n">
-        <v>16296858000</v>
+        <v>2805888000</v>
       </c>
     </row>
   </sheetData>
@@ -4040,192 +4040,192 @@
       </c>
       <c r="DJ1" t="inlineStr">
         <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EV1" t="inlineStr">
@@ -4329,7 +4329,7 @@
         <v>8</v>
       </c>
       <c r="V2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="W2" t="n">
         <v>1735603200</v>
@@ -4379,7 +4379,7 @@
         <v>4.89</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.174</v>
+        <v>1.128</v>
       </c>
       <c r="AM2" t="n">
         <v>3.1807232</v>
@@ -4391,7 +4391,7 @@
         <v>2210923</v>
       </c>
       <c r="AP2" t="n">
-        <v>1006018</v>
+        <v>269062</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -4433,10 +4433,10 @@
         <v>0.32832018</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.6478</v>
+        <v>2.64</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.0842</v>
+        <v>3.0164</v>
       </c>
       <c r="BF2" t="n">
         <v>0</v>
@@ -4468,7 +4468,7 @@
         <v>0.73894995</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.025409998</v>
+        <v>0.0255</v>
       </c>
       <c r="BP2" t="n">
         <v>3792541000</v>
@@ -4512,10 +4512,10 @@
         <v>15.501</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0.1372549</v>
+        <v>-0.15384614</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="CE2" t="n">
         <v>0.103306</v>
@@ -4630,141 +4630,141 @@
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>finmb_4492768</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>HOPSON DEV HOLD</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>Hopson Development Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>946949400000</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.00999999</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>2.62 - 2.69</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DX2" t="n">
+        <v>269062</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0.03000021</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0.011494334</v>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>2.61 - 4.28</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
           <t>PREPRE</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>HOPSON DEV HOLD</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>Hopson Development Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
+      <c r="EC2" t="n">
+        <v>-1.6400001</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.38317758</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-15.384615</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>1743153151</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>1743153151</v>
+      </c>
+      <c r="EH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>-0.3764</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>-0.12478451</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EQ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>0.38022774</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="ET2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DN2" t="n">
+      <c r="EU2" t="n">
         <v>1774944503</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>finmb_4492768</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DS2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>946949400000</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0.00999999</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>2.62 - 2.69</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EB2" t="n">
-        <v>1006018</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0.03000021</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.011494334</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>2.61 - 4.28</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>-1.6400001</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.38317758</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-13.72549</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1743153151</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1743153151</v>
-      </c>
-      <c r="EK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>-0.007799864</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>-0.0029457905</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>-0.4441998</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>-0.14402433</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>0.38022774</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>2.64</v>
       </c>
       <c r="EV2" t="inlineStr"/>
     </row>
